--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE284D9C-0848-49BD-BDB0-C79CE69792CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>

--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE284D9C-0848-49BD-BDB0-C79CE69792CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E4B960-6DBA-420D-A44E-50303E9DC8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>T0 Lancement : 03/09/26   |   T1 Audit : 06/10/26   |   T2 PDR : 20/11/26   |   T3 CDR + Mini salon : 08/01/27</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>Issam</t>
+  </si>
+  <si>
+    <t>Alexandre</t>
+  </si>
+  <si>
+    <t>Choix des composants</t>
   </si>
 </sst>
 </file>
@@ -440,6 +446,241 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>65484</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>107156</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Connecteur droit avec flèche 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E16A9E83-720A-6928-D4AB-A9CC81B3F513}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9936163" y="2232819"/>
+          <a:ext cx="184149" cy="719931"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Connecteur droit avec flèche 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F10B409D-C561-B463-1064-DAD2A8BD644E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10810875" y="2238375"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>35719</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>136921</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Connecteur droit avec flèche 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BE8F536-4221-4759-ABAF-F1C30E67D3FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9948863" y="2255044"/>
+          <a:ext cx="141684" cy="906065"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>201613</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>111919</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="Connecteur droit avec flèche 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37B8E5EF-9C59-4691-8A54-6A3F7BBFC3E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9945688" y="2255044"/>
+          <a:ext cx="141287" cy="1497806"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -619,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -811,7 +1052,7 @@
         <v>46268</v>
       </c>
       <c r="F6" s="7">
-        <f t="shared" ref="F6:F30" si="0">E6-D6+1</f>
+        <f t="shared" ref="F6:F31" si="0">E6-D6+1</f>
         <v>1</v>
       </c>
       <c r="G6" s="8"/>
@@ -1077,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D13" s="12">
         <v>46293</v>
@@ -1227,23 +1468,23 @@
       <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
     </row>
-    <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A17" s="18"/>
       <c r="B17" s="10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D17" s="12">
-        <v>46301</v>
+        <v>46294</v>
       </c>
       <c r="E17" s="12">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="F17" s="13">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <f>E17-D17+1</f>
+        <v>17</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
@@ -1266,10 +1507,10 @@
       <c r="Y17" s="8"/>
       <c r="Z17" s="8"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18"/>
       <c r="B18" s="10" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>27</v>
@@ -1278,11 +1519,11 @@
         <v>46301</v>
       </c>
       <c r="E18" s="12">
-        <v>46329</v>
+        <v>46314</v>
       </c>
       <c r="F18" s="13">
-        <f>E18-D18+1-7</f>
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -1308,20 +1549,20 @@
     <row r="19" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A19" s="18"/>
       <c r="B19" s="10" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="12">
-        <v>46308</v>
+        <v>46301</v>
       </c>
       <c r="E19" s="12">
-        <v>46314</v>
+        <v>46329</v>
       </c>
       <c r="F19" s="13">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>E19-D19+1-7</f>
+        <v>22</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -1347,20 +1588,20 @@
     <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20" s="18"/>
       <c r="B20" s="10" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D20" s="12">
-        <v>46329</v>
+        <v>46308</v>
       </c>
       <c r="E20" s="12">
-        <v>46345</v>
+        <v>46314</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -1386,20 +1627,20 @@
     <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" s="18"/>
       <c r="B21" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D21" s="12">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="E21" s="12">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="F21" s="13">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -1423,20 +1664,22 @@
       <c r="Z21" s="8"/>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="6">
+      <c r="A22" s="18"/>
+      <c r="B22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="12">
+        <v>46328</v>
+      </c>
+      <c r="E22" s="12">
         <v>46346</v>
       </c>
-      <c r="E22" s="6">
-        <v>46346</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="F22" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -1460,24 +1703,20 @@
       <c r="Z22" s="8"/>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="12">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="6">
         <v>46346</v>
       </c>
-      <c r="E23" s="12">
-        <v>46347</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="E23" s="6">
+        <v>46346</v>
+      </c>
+      <c r="F23" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -1501,22 +1740,24 @@
       <c r="Z23" s="8"/>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A24" s="15"/>
+      <c r="A24" s="15" t="s">
+        <v>16</v>
+      </c>
       <c r="B24" s="10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="12">
-        <v>46349</v>
+        <v>46346</v>
       </c>
       <c r="E24" s="12">
-        <v>46391</v>
+        <v>46347</v>
       </c>
       <c r="F24" s="13">
-        <f>E24-D24+1-14</f>
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -1542,19 +1783,19 @@
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25" s="15"/>
       <c r="B25" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="12">
-        <v>46350</v>
+        <v>46349</v>
       </c>
       <c r="E25" s="12">
-        <v>46392</v>
+        <v>46391</v>
       </c>
       <c r="F25" s="13">
-        <f t="shared" ref="F25:F26" si="1">E25-D25+1-14</f>
+        <f>E25-D25+1-14</f>
         <v>29</v>
       </c>
       <c r="G25" s="8"/>
@@ -1581,20 +1822,20 @@
     <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26" s="15"/>
       <c r="B26" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D26" s="12">
-        <v>46371</v>
+        <v>46350</v>
       </c>
       <c r="E26" s="12">
         <v>46392</v>
       </c>
       <c r="F26" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f t="shared" ref="F26:F27" si="1">E26-D26+1-14</f>
+        <v>29</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -1620,20 +1861,20 @@
     <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27" s="15"/>
       <c r="B27" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="12">
-        <v>46391</v>
+        <v>46371</v>
       </c>
       <c r="E27" s="12">
-        <v>46394</v>
+        <v>46392</v>
       </c>
       <c r="F27" s="13">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
@@ -1659,20 +1900,20 @@
     <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28" s="15"/>
       <c r="B28" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="12">
-        <v>46371</v>
+        <v>46391</v>
       </c>
       <c r="E28" s="12">
         <v>46394</v>
       </c>
       <c r="F28" s="13">
-        <f>E28-D28+1-14</f>
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -1698,7 +1939,7 @@
     <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29" s="15"/>
       <c r="B29" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>27</v>
@@ -1735,20 +1976,22 @@
       <c r="Z29" s="8"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="6">
-        <v>46395</v>
-      </c>
-      <c r="E30" s="6">
-        <v>46395</v>
-      </c>
-      <c r="F30" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="A30" s="15"/>
+      <c r="B30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="12">
+        <v>46371</v>
+      </c>
+      <c r="E30" s="12">
+        <v>46394</v>
+      </c>
+      <c r="F30" s="13">
+        <f>E30-D30+1-14</f>
+        <v>10</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
@@ -1771,30 +2014,68 @@
       <c r="Y30" s="8"/>
       <c r="Z30" s="8"/>
     </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="6">
+        <v>46395</v>
+      </c>
+      <c r="E31" s="6">
+        <v>46395</v>
+      </c>
+      <c r="F31" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="A24:A30"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A16:A22"/>
   </mergeCells>
-  <conditionalFormatting sqref="G6:Z6 G15:Z15 G22:Z22 G30:Z30">
+  <conditionalFormatting sqref="G6:Z6 G15:Z15 G23:Z23 G31:Z31">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(G$5&lt;=$E6,(G$5+6)&gt;=$D6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:Z14 G16:Z21 G23:Z29">
+  <conditionalFormatting sqref="G7:Z14 G16:Z22 G24:Z30">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND(G$5&lt;=$E7,(G$5+6)&gt;=$D7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C16:C21 C23:C29 C7:C14 C13" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="C16:C22 C24:C30 C7:C14 C13" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Alexandre,Issam,Maud,Simon,Tous,À définir"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ADRAPEAU/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E4B960-6DBA-420D-A44E-50303E9DC8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543592C2-1B4F-C040-9AD3-DB48701AEFE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -36,122 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
-  <si>
-    <t>T0 Lancement : 03/09/26   |   T1 Audit : 06/10/26   |   T2 PDR : 20/11/26   |   T3 CDR + Mini salon : 08/01/27</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>Phase</t>
   </si>
   <si>
-    <t>Tâche</t>
-  </si>
-  <si>
-    <t>Responsable</t>
-  </si>
-  <si>
-    <t>Début</t>
-  </si>
-  <si>
-    <t>Fin</t>
-  </si>
-  <si>
-    <t>Durée (j)</t>
-  </si>
-  <si>
-    <t>T0 — Lancement du projet</t>
-  </si>
-  <si>
-    <t>Phase A — Cadrage &amp; analyse</t>
-  </si>
-  <si>
-    <t>Rédiger le rapport technique T1 (Audit)</t>
-  </si>
-  <si>
-    <t>T1 — Audit</t>
-  </si>
-  <si>
-    <t>Phase B — Conception &amp; solutions techniques</t>
-  </si>
-  <si>
-    <t>Avancer la conception mécanique 3D du système (dimensionnement, architecture)</t>
-  </si>
-  <si>
-    <t>Justifier les solutions techniques retenues + volet RSE</t>
-  </si>
-  <si>
-    <t>Revue préliminaire des HVA + mise à jour du rapport technique (PDR)</t>
-  </si>
-  <si>
-    <t>T2 — PDR</t>
-  </si>
-  <si>
-    <t>Phase C — Intégration &amp; validation HVA</t>
-  </si>
-  <si>
-    <t>Fabriquer / assembler le système (mécanique + électronique)</t>
-  </si>
-  <si>
-    <t>Développer et intégrer les fonctions HVA retenues</t>
-  </si>
-  <si>
-    <t>Tester chaque fonction par rapport aux exigences (matrice de conformité)</t>
-  </si>
-  <si>
-    <t>Résoudre les défauts identifiés</t>
-  </si>
-  <si>
-    <t>Préparer la démonstration des HVA (CDR) + vidéo marketing (anglais) pour le mini salon</t>
-  </si>
-  <si>
-    <t>Rédiger le rapport technique final S1 + auto-évaluation</t>
-  </si>
-  <si>
-    <t>T3 — CDR + Mini salon</t>
-  </si>
-  <si>
-    <t>Détailler le Gantt de la phase T1</t>
-  </si>
-  <si>
-    <t>Gantt Gyrobot</t>
-  </si>
-  <si>
-    <t>Tous</t>
-  </si>
-  <si>
-    <t>À définir</t>
-  </si>
-  <si>
-    <t>Identifier les fonctions HVA du projet</t>
-  </si>
-  <si>
-    <t>Mettre à jour GitLab</t>
-  </si>
-  <si>
-    <t>Générer et évaluer des solutions techniques pour chaque fonction</t>
-  </si>
-  <si>
-    <t>Sélectionner et commander les composants nécessaires</t>
-  </si>
-  <si>
-    <t>Détailler le Gantt de la phase T2</t>
-  </si>
-  <si>
-    <t>Faire le ReadMe</t>
-  </si>
-  <si>
-    <t>Faire les differents diagrammes</t>
-  </si>
-  <si>
-    <t>Approche RSE</t>
-  </si>
-  <si>
-    <t>Faire le PPT (chemin critique)</t>
-  </si>
-  <si>
-    <t>Cahier des charges</t>
-  </si>
-  <si>
     <t>Simon</t>
   </si>
   <si>
@@ -164,7 +42,118 @@
     <t>Alexandre</t>
   </si>
   <si>
-    <t>Choix des composants</t>
+    <t>Gyrobot Gantt Chart</t>
+  </si>
+  <si>
+    <t>T0 Kickoff: 09/03/26   |   T1 Audit: 10/06/26   |   T2 PDR : 20/11/26   |   T3 CDR + Mini trade show : 08/01/27</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Duration (days)</t>
+  </si>
+  <si>
+    <t>T0: Project kickoff</t>
+  </si>
+  <si>
+    <t>Update GitLab</t>
+  </si>
+  <si>
+    <t>Write the ReadMe</t>
+  </si>
+  <si>
+    <t>Create the various diagrams</t>
+  </si>
+  <si>
+    <t>Identify the project's HVA functions</t>
+  </si>
+  <si>
+    <t>Specifications document</t>
+  </si>
+  <si>
+    <t>CSR approach</t>
+  </si>
+  <si>
+    <t>Write the T1 technical report (Audit)</t>
+  </si>
+  <si>
+    <t>Prepare the PPT (critical path)</t>
+  </si>
+  <si>
+    <t>Phase A: Scoping and Analysis</t>
+  </si>
+  <si>
+    <t>Phase B: Design and Technical Solutions</t>
+  </si>
+  <si>
+    <t>Phase C: Integration and HVA Validation</t>
+  </si>
+  <si>
+    <t>T1: Audit</t>
+  </si>
+  <si>
+    <t>Detail the Phase T1 Gantt chart</t>
+  </si>
+  <si>
+    <t>Select components and place order</t>
+  </si>
+  <si>
+    <t>Generate and evaluate technical solutions for each function</t>
+  </si>
+  <si>
+    <t>Advance the system's 3D mechanical design (sizing, architecture)</t>
+  </si>
+  <si>
+    <t>Justify the chosen technical solutions + CSR component</t>
+  </si>
+  <si>
+    <t>Preliminary HVA review + technical report update (PDR)</t>
+  </si>
+  <si>
+    <t>T2: PDR</t>
+  </si>
+  <si>
+    <t>Detail the Phase T2 Gantt chart</t>
+  </si>
+  <si>
+    <t>Manufacture / assemble the system (mechanical + electronics)</t>
+  </si>
+  <si>
+    <t>Develop and integrate the selected HVA functions</t>
+  </si>
+  <si>
+    <t>Test each function against requirements (compliance matrix)</t>
+  </si>
+  <si>
+    <t>Fix identified defects</t>
+  </si>
+  <si>
+    <t>Prepare the HVA demonstration (CDR) + marketing video (English) for the mini trade show</t>
+  </si>
+  <si>
+    <t>Write the final S1 technical report</t>
+  </si>
+  <si>
+    <t>T3: CDR + Mini trade show</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>To be defined</t>
+  </si>
+  <si>
+    <t>Maud &amp; Simon</t>
   </si>
 </sst>
 </file>
@@ -272,7 +261,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -295,11 +284,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -343,8 +369,17 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -678,6 +713,242 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>132080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>20320</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>71120</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Connecteur droit avec flèche 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06C684B5-90E3-BA47-9B79-1C6021C29EC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11866880" y="3850640"/>
+          <a:ext cx="711200" cy="711200"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>132080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>132080</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="Connecteur droit avec flèche 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18F9518A-DEF7-BA48-8B02-92E2022936F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11866880" y="3850640"/>
+          <a:ext cx="721360" cy="772160"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="Connecteur droit avec flèche 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2925C26F-A4BA-0D4C-AAF6-FDB0277E2F5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13583920" y="4419600"/>
+          <a:ext cx="10160" cy="833120"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>142240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>142240</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Connecteur droit avec flèche 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2F98D4B-09EC-584A-90E0-33AC39FB6162}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13583920" y="4439920"/>
+          <a:ext cx="10160" cy="965200"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -860,20 +1131,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Z30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="81.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="26" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="26" width="4.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -901,9 +1172,9 @@
       <c r="Y1" s="16"/>
       <c r="Z1" s="16"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -931,13 +1202,13 @@
       <c r="Y2" s="17"/>
       <c r="Z2" s="17"/>
     </row>
-    <row r="3" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+    <row r="3" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
@@ -959,24 +1230,24 @@
       <c r="Y3" s="14"/>
       <c r="Z3" s="14"/>
     </row>
-    <row r="5" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2">
         <v>46265</v>
@@ -1039,10 +1310,10 @@
         <v>46398</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="6">
@@ -1052,7 +1323,7 @@
         <v>46268</v>
       </c>
       <c r="F6" s="7">
-        <f t="shared" ref="F6:F31" si="0">E6-D6+1</f>
+        <f t="shared" ref="F6:F30" si="0">E6-D6+1</f>
         <v>1</v>
       </c>
       <c r="G6" s="8"/>
@@ -1076,15 +1347,15 @@
       <c r="Y6" s="8"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D7" s="12">
         <v>46268</v>
@@ -1093,7 +1364,7 @@
         <v>46300</v>
       </c>
       <c r="F7" s="13">
-        <f>E7-D7+1</f>
+        <f t="shared" ref="F7:F13" si="1">E7-D7+1</f>
         <v>33</v>
       </c>
       <c r="G7" s="8"/>
@@ -1117,13 +1388,13 @@
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A8" s="19"/>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
       <c r="B8" s="10" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D8" s="12">
         <v>46268</v>
@@ -1132,7 +1403,7 @@
         <v>46273</v>
       </c>
       <c r="F8" s="13">
-        <f>E8-D8+1</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="G8" s="8"/>
@@ -1156,13 +1427,13 @@
       <c r="Y8" s="8"/>
       <c r="Z8" s="8"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A9" s="19"/>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
       <c r="B9" s="10" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D9" s="12">
         <v>46269</v>
@@ -1171,7 +1442,7 @@
         <v>46287</v>
       </c>
       <c r="F9" s="13">
-        <f>E9-D9+1</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="G9" s="8"/>
@@ -1195,13 +1466,13 @@
       <c r="Y9" s="8"/>
       <c r="Z9" s="8"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A10" s="19"/>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
       <c r="B10" s="10" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D10" s="12">
         <v>46280</v>
@@ -1210,7 +1481,7 @@
         <v>46294</v>
       </c>
       <c r="F10" s="13">
-        <f>E10-D10+1</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="G10" s="8"/>
@@ -1234,13 +1505,13 @@
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
       <c r="B11" s="10" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D11" s="12">
         <v>46286</v>
@@ -1249,7 +1520,7 @@
         <v>46295</v>
       </c>
       <c r="F11" s="13">
-        <f>E11-D11+1</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="G11" s="8"/>
@@ -1273,13 +1544,13 @@
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A12" s="19"/>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
       <c r="B12" s="10" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D12" s="12">
         <v>46295</v>
@@ -1288,7 +1559,7 @@
         <v>46299</v>
       </c>
       <c r="F12" s="13">
-        <f>E12-D12+1</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="G12" s="8"/>
@@ -1312,13 +1583,13 @@
       <c r="Y12" s="8"/>
       <c r="Z12" s="8"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A13" s="19"/>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
       <c r="B13" s="10" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D13" s="12">
         <v>46293</v>
@@ -1327,7 +1598,7 @@
         <v>46300</v>
       </c>
       <c r="F13" s="13">
-        <f>E13-D13+1</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="G13" s="8"/>
@@ -1351,13 +1622,13 @@
       <c r="Y13" s="8"/>
       <c r="Z13" s="8"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A14" s="19"/>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A14" s="21"/>
       <c r="B14" s="10" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D14" s="12">
         <v>46295</v>
@@ -1390,10 +1661,10 @@
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="6">
@@ -1427,15 +1698,15 @@
       <c r="Y15" s="8"/>
       <c r="Z15" s="8"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D16" s="12">
         <v>46301</v>
@@ -1468,13 +1739,13 @@
       <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" s="18"/>
       <c r="B17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="D17" s="12">
         <v>46294</v>
@@ -1507,13 +1778,13 @@
       <c r="Y17" s="8"/>
       <c r="Z17" s="8"/>
     </row>
-    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="18"/>
       <c r="B18" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D18" s="12">
         <v>46301</v>
@@ -1546,23 +1817,23 @@
       <c r="Y18" s="8"/>
       <c r="Z18" s="8"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="18"/>
       <c r="B19" s="10" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D19" s="12">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="E19" s="12">
         <v>46329</v>
       </c>
       <c r="F19" s="13">
         <f>E19-D19+1-7</f>
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -1585,23 +1856,23 @@
       <c r="Y19" s="8"/>
       <c r="Z19" s="8"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" s="18"/>
       <c r="B20" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D20" s="12">
-        <v>46308</v>
+        <v>46329</v>
       </c>
       <c r="E20" s="12">
-        <v>46314</v>
+        <v>46345</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
@@ -1624,23 +1895,23 @@
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" s="18"/>
       <c r="B21" s="10" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D21" s="12">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="E21" s="12">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="F21" s="13">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
@@ -1663,23 +1934,21 @@
       <c r="Y21" s="8"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
-      <c r="B22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="12">
-        <v>46328</v>
-      </c>
-      <c r="E22" s="12">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="6">
         <v>46346</v>
       </c>
-      <c r="F22" s="13">
+      <c r="E22" s="6">
+        <v>46346</v>
+      </c>
+      <c r="F22" s="7">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -1702,21 +1971,25 @@
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="6">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A23" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="12">
         <v>46346</v>
       </c>
-      <c r="E23" s="6">
-        <v>46346</v>
-      </c>
-      <c r="F23" s="7">
+      <c r="E23" s="12">
+        <v>46347</v>
+      </c>
+      <c r="F23" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -1739,25 +2012,23 @@
       <c r="Y23" s="8"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A24" s="15" t="s">
-        <v>16</v>
-      </c>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A24" s="15"/>
       <c r="B24" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D24" s="12">
-        <v>46346</v>
+        <v>46349</v>
       </c>
       <c r="E24" s="12">
-        <v>46347</v>
+        <v>46376</v>
       </c>
       <c r="F24" s="13">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f>E24-D24+1-14</f>
+        <v>14</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -1780,22 +2051,22 @@
       <c r="Y24" s="8"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
       <c r="B25" s="10" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D25" s="12">
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="E25" s="12">
-        <v>46391</v>
+        <v>46392</v>
       </c>
       <c r="F25" s="13">
-        <f>E25-D25+1-14</f>
+        <f t="shared" ref="F25:F26" si="2">E25-D25+1-14</f>
         <v>29</v>
       </c>
       <c r="G25" s="8"/>
@@ -1819,23 +2090,23 @@
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="15"/>
       <c r="B26" s="10" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D26" s="12">
-        <v>46350</v>
+        <v>46371</v>
       </c>
       <c r="E26" s="12">
         <v>46392</v>
       </c>
       <c r="F26" s="13">
-        <f t="shared" ref="F26:F27" si="1">E26-D26+1-14</f>
-        <v>29</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
@@ -1858,23 +2129,23 @@
       <c r="Y26" s="8"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
       <c r="B27" s="10" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D27" s="12">
-        <v>46371</v>
+        <v>46391</v>
       </c>
       <c r="E27" s="12">
-        <v>46392</v>
+        <v>46394</v>
       </c>
       <c r="F27" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
@@ -1897,23 +2168,23 @@
       <c r="Y27" s="8"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="10" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D28" s="12">
-        <v>46391</v>
+        <v>46371</v>
       </c>
       <c r="E28" s="12">
         <v>46394</v>
       </c>
       <c r="F28" s="13">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>E28-D28+1-14</f>
+        <v>10</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
@@ -1936,13 +2207,13 @@
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
       <c r="B29" s="10" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D29" s="12">
         <v>46371</v>
@@ -1975,23 +2246,21 @@
       <c r="Y29" s="8"/>
       <c r="Z29" s="8"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A30" s="15"/>
-      <c r="B30" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="12">
-        <v>46371</v>
-      </c>
-      <c r="E30" s="12">
-        <v>46394</v>
-      </c>
-      <c r="F30" s="13">
-        <f>E30-D30+1-14</f>
-        <v>10</v>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="6">
+        <v>46395</v>
+      </c>
+      <c r="E30" s="6">
+        <v>46395</v>
+      </c>
+      <c r="F30" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
@@ -2014,64 +2283,28 @@
       <c r="Y30" s="8"/>
       <c r="Z30" s="8"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="6">
-        <v>46395</v>
-      </c>
-      <c r="E31" s="6">
-        <v>46395</v>
-      </c>
-      <c r="F31" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="8"/>
-      <c r="Z31" s="8"/>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A24:A30"/>
+  <mergeCells count="6">
+    <mergeCell ref="A23:A29"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
-  <conditionalFormatting sqref="G6:Z6 G15:Z15 G23:Z23 G31:Z31">
+  <conditionalFormatting sqref="G6:Z6 G15:Z15 G22:Z22 G30:Z30">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(G$5&lt;=$E6,(G$5+6)&gt;=$D6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:Z14 G16:Z22 G24:Z30">
+  <conditionalFormatting sqref="G7:Z14 G16:Z21 G23:Z29">
     <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND(G$5&lt;=$E7,(G$5+6)&gt;=$D7)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="C16:C22 C24:C30 C7:C14 C13" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Alexandre,Issam,Maud,Simon,Tous,À définir"</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" sqref="C16:C21 C7:C14 C23:C29" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Alexandre,Issam,Maud,Simon,All,To be defined"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Gantt.xlsx
+++ b/Gantt.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ADRAPEAU/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Documents\Polytech\GPSE\4A\Projet\gyrobot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543592C2-1B4F-C040-9AD3-DB48701AEFE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4574AD1D-ED12-4C6B-A373-59F3B48F8CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -1132,17 +1143,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" customWidth="1"/>
+    <col min="2" max="2" width="57.33203125" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="26" width="4.5" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" customWidth="1"/>
+    <col min="7" max="26" width="4.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>5</v>
       </c>
@@ -1172,7 +1183,7 @@
       <c r="Y1" s="16"/>
       <c r="Z1" s="16"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>6</v>
       </c>
@@ -1202,7 +1213,7 @@
       <c r="Y2" s="17"/>
       <c r="Z2" s="17"/>
     </row>
-    <row r="3" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -1230,7 +1241,7 @@
       <c r="Y3" s="14"/>
       <c r="Z3" s="14"/>
     </row>
-    <row r="5" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1321,7 @@
         <v>46398</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
         <v>12</v>
@@ -1347,7 +1358,7 @@
       <c r="Y6" s="8"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>21</v>
       </c>
@@ -1388,7 +1399,7 @@
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="20"/>
       <c r="B8" s="10" t="s">
         <v>14</v>
@@ -1427,7 +1438,7 @@
       <c r="Y8" s="8"/>
       <c r="Z8" s="8"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="20"/>
       <c r="B9" s="10" t="s">
         <v>15</v>
@@ -1466,7 +1477,7 @@
       <c r="Y9" s="8"/>
       <c r="Z9" s="8"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" s="20"/>
       <c r="B10" s="10" t="s">
         <v>16</v>
@@ -1505,7 +1516,7 @@
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="20"/>
       <c r="B11" s="10" t="s">
         <v>17</v>
@@ -1544,7 +1555,7 @@
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="20"/>
       <c r="B12" s="10" t="s">
         <v>18</v>
@@ -1583,7 +1594,7 @@
       <c r="Y12" s="8"/>
       <c r="Z12" s="8"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="B13" s="10" t="s">
         <v>19</v>
@@ -1622,7 +1633,7 @@
       <c r="Y13" s="8"/>
       <c r="Z13" s="8"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="21"/>
       <c r="B14" s="10" t="s">
         <v>20</v>
@@ -1661,7 +1672,7 @@
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="5" t="s">
         <v>24</v>
@@ -1698,7 +1709,7 @@
       <c r="Y15" s="8"/>
       <c r="Z15" s="8"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>22</v>
       </c>
@@ -1739,7 +1750,7 @@
       <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
       <c r="B17" s="10" t="s">
         <v>26</v>
@@ -1778,7 +1789,7 @@
       <c r="Y17" s="8"/>
       <c r="Z17" s="8"/>
     </row>
-    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18"/>
       <c r="B18" s="10" t="s">
         <v>27</v>
@@ -1817,7 +1828,7 @@
       <c r="Y18" s="8"/>
       <c r="Z18" s="8"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="18"/>
       <c r="B19" s="10" t="s">
         <v>28</v>
@@ -1856,7 +1867,7 @@
       <c r="Y19" s="8"/>
       <c r="Z19" s="8"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A20" s="18"/>
       <c r="B20" s="10" t="s">
         <v>29</v>
@@ -1895,7 +1906,7 @@
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A21" s="18"/>
       <c r="B21" s="10" t="s">
         <v>30</v>
@@ -1934,7 +1945,7 @@
       <c r="Y21" s="8"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="5" t="s">
         <v>31</v>
@@ -1971,7 +1982,7 @@
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>23</v>
       </c>
@@ -2012,7 +2023,7 @@
       <c r="Y23" s="8"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="10" t="s">
         <v>33</v>
@@ -2051,7 +2062,7 @@
       <c r="Y24" s="8"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A25" s="15"/>
       <c r="B25" s="10" t="s">
         <v>34</v>
@@ -2090,7 +2101,7 @@
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="10" t="s">
         <v>35</v>
@@ -2129,7 +2140,7 @@
       <c r="Y26" s="8"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A27" s="15"/>
       <c r="B27" s="10" t="s">
         <v>36</v>
@@ -2168,7 +2179,7 @@
       <c r="Y27" s="8"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="10" t="s">
         <v>37</v>
@@ -2207,7 +2218,7 @@
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29" s="15"/>
       <c r="B29" s="10" t="s">
         <v>38</v>
@@ -2246,7 +2257,7 @@
       <c r="Y29" s="8"/>
       <c r="Z29" s="8"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="5" t="s">
         <v>39</v>
@@ -2308,7 +2319,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>